--- a/mixs-templates/Mimag_plus_combinations/MimagHumanOral.xlsx
+++ b/mixs-templates/Mimag_plus_combinations/MimagHumanOral.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP1"/>
+  <dimension ref="A1:CR1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,265 +624,275 @@
       </c>
       <c r="AP1" t="inlineStr">
         <is>
+          <t>marker_gene_recov</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>marker_gene_recov_sw</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
           <t>pos_cont_type</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>feat_pred</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>compl_software</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>env_local_scale</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>samp_mat_process</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>sim_search_meth</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>depth</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>samp_collect_method</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>compl_appr</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>env_medium</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>samp_taxon_id</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>geo_loc_name</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>collection_date</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>seq_meth</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>lat_lon</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>elev</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>env_broad_scale</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>tax_class</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>experimental_factor</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>associated_resource</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>sop</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>nose_mouth_teeth_throat_disord</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>time_last_toothbrush</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>host_subject_id</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>host_age</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>host_sex</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>host_disease_stat</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>ihmc_medication_code</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>chem_administration</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>host_body_site</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>host_body_product</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>host_tot_mass</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>host_height</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>host_diet</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>host_last_meal</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>host_fam_rel</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>host_genotype</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>host_phenotype</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>host_body_temp</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>host_body_mass_index</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>ethnicity</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>host_occupation</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>medic_hist_perform</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>host_pulse</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>perturbation</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>salinity</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>oxy_stat_samp</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>organism_count</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>samp_store_temp</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>samp_store_dur</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>host_symbiont</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>samp_store_loc</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>misc_param</t>
         </is>
@@ -914,10 +924,10 @@
     <dataValidation sqref="AK2:AK1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"16S rRNA gene,multi-marker approach,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="AX2:AX1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AZ2:AZ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"marker gene,other,reference based"</formula1>
     </dataValidation>
-    <dataValidation sqref="CJ2:CJ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CL2:CL1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"aerobic,anaerobic,other"</formula1>
     </dataValidation>
   </dataValidations>
